--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_171_R18.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_171_R18.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4507</v>
+        <v>4.947</v>
       </c>
       <c r="E2" t="n">
-        <v>2.4934</v>
+        <v>3.5864</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9573</v>
+        <v>1.3606</v>
       </c>
       <c r="G2" t="n">
         <v>-0.2182</v>
@@ -610,13 +610,13 @@
         <v>2.5515</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.563</v>
+        <v>-0.0668</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.731</v>
+        <v>0.362</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.832</v>
+        <v>-0.4288</v>
       </c>
       <c r="V2" t="n">
         <v>2.6805</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9836</v>
+        <v>3.2195</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7766</v>
+        <v>3.0125</v>
       </c>
       <c r="F3" t="n">
         <v>0.2071</v>
@@ -688,10 +688,10 @@
         <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0747</v>
+        <v>0.3106</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0589</v>
+        <v>0.177</v>
       </c>
       <c r="U3" t="n">
         <v>0.1336</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4219</v>
+        <v>2.2277</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1985</v>
+        <v>2.2731</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2234</v>
+        <v>-0.0454</v>
       </c>
       <c r="G4" t="n">
         <v>2.4959</v>
@@ -766,13 +766,13 @@
         <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4261</v>
+        <v>0.232</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0633</v>
+        <v>0.1379</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3629</v>
+        <v>0.094</v>
       </c>
       <c r="V4" t="n">
         <v>-1.8919</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1639</v>
+        <v>0.3737</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.8845</v>
+        <v>-1.5739</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0484</v>
+        <v>1.9476</v>
       </c>
       <c r="G5" t="n">
         <v>-1.0753</v>
@@ -844,13 +844,13 @@
         <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6216</v>
+        <v>-0.4118</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4323</v>
+        <v>-0.1217</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1893</v>
+        <v>-0.2902</v>
       </c>
       <c r="V5" t="n">
         <v>1.8608</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1192</v>
+        <v>-0.4705</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.482</v>
+        <v>-2.0718</v>
       </c>
       <c r="F6" t="n">
         <v>1.6012</v>
@@ -922,10 +922,10 @@
         <v>1.6237</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0262</v>
+        <v>0.4364</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9164</v>
+        <v>0.3266</v>
       </c>
       <c r="U6" t="n">
         <v>0.1098</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. DA SILVA</t>
+          <t>N. GIFFEY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1995</v>
+        <v>-1.5328</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6763</v>
+        <v>-2.3344</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5232</v>
+        <v>0.8017</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9842</v>
+        <v>-0.0565</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9341</v>
+        <v>0.6963</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0501</v>
+        <v>-0.7528</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7427</v>
+        <v>0.1579</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6322</v>
+        <v>0.9075</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1104</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7269</v>
+        <v>-0.2144</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5664</v>
+        <v>-0.2112</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1605</v>
+        <v>-0.0033</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4639</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q7" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8556</v>
+        <v>0.6959</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2486</v>
+        <v>0.1474</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9006</v>
+        <v>-0.1729</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6519</v>
+        <v>0.3203</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. GIFFEY</t>
+          <t>O. DA SILVA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7179</v>
+        <v>-1.7488</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4524</v>
+        <v>-1.4273</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7345</v>
+        <v>-0.3216</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0565</v>
+        <v>-0.9842</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6963</v>
+        <v>-0.9341</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7528</v>
+        <v>-0.0501</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1579</v>
+        <v>0.7427</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9075</v>
+        <v>0.6322</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7495000000000001</v>
+        <v>0.1104</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2144</v>
+        <v>-1.7269</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2112</v>
+        <v>-1.5664</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0033</v>
+        <v>-0.1605</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.6237</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q8" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6959</v>
+        <v>1.8556</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0378</v>
+        <v>-0.3007</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2908</v>
+        <v>0.1496</v>
       </c>
       <c r="U8" t="n">
-        <v>0.253</v>
+        <v>-0.4503</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4297</v>
+        <v>-2.3544</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5139</v>
+        <v>-1.2033</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9157999999999999</v>
+        <v>-1.151</v>
       </c>
       <c r="G9" t="n">
         <v>0.3641</v>
@@ -1156,13 +1156,13 @@
         <v>1.1598</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5619</v>
+        <v>-0.4865</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8136</v>
+        <v>-0.503</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2517</v>
+        <v>0.0165</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0722</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>W. GABRIEL</t>
+          <t>V. LUCIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8709</v>
+        <v>-2.7462</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.461</v>
+        <v>-0.3229</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.41</v>
+        <v>-2.4232</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0153</v>
+        <v>-0.7050999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8079</v>
+        <v>-0.8522999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2074</v>
+        <v>0.1472</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.622</v>
+        <v>1.0434</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7324000000000001</v>
+        <v>0.5783</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1104</v>
+        <v>0.465</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3933</v>
+        <v>-1.7484</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0755</v>
+        <v>-1.4306</v>
       </c>
       <c r="O10" t="n">
         <v>-0.3178</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7938</v>
+        <v>-1.0359</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8259</v>
+        <v>-0.5777</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0321</v>
+        <v>-0.4582</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.6495</v>
+        <v>-2.3969</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.5051</v>
+        <v>-0.7886</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1444</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0923</v>
+        <v>-3.5059</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9321</v>
+        <v>-3.2112</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1602</v>
+        <v>-0.2946</v>
       </c>
       <c r="G11" t="n">
         <v>-1.4641</v>
@@ -1312,13 +1312,13 @@
         <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0677</v>
+        <v>-0.3459</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1968</v>
+        <v>-0.0824</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1291</v>
+        <v>-0.2636</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5361</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V. LUCIC</t>
+          <t>W. GABRIEL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.1987</v>
+        <v>-3.6048</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7082000000000001</v>
+        <v>-2.094</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.4904</v>
+        <v>-1.5108</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.7050999999999999</v>
+        <v>-1.0153</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8522999999999999</v>
+        <v>-0.8079</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1472</v>
+        <v>-0.2074</v>
       </c>
       <c r="J12" t="n">
-        <v>1.0434</v>
+        <v>-0.622</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5783</v>
+        <v>-0.7324000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>0.465</v>
+        <v>0.1104</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.7484</v>
+        <v>-0.3933</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.4306</v>
+        <v>-0.0755</v>
       </c>
       <c r="O12" t="n">
         <v>-0.3178</v>
       </c>
       <c r="P12" t="n">
-        <v>1.3917</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.4883</v>
+        <v>0.06</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.963</v>
+        <v>0.1928</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5254</v>
+        <v>-0.1329</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.3969</v>
+        <v>-2.6495</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.7886</v>
+        <v>-0.5051</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.6083</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.4726</v>
+        <v>-3.9</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.6378</v>
+        <v>-4.166</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1652</v>
+        <v>0.266</v>
       </c>
       <c r="G13" t="n">
         <v>-1.1353</v>
@@ -1468,13 +1468,13 @@
         <v>1.1598</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0179</v>
+        <v>-0.4452</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2987</v>
+        <v>0.1731</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7191</v>
+        <v>-0.6183</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-9.8423</v>
+        <v>-9.095500000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-10.2797</v>
+        <v>-9.532800000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4374999999999991</v>
+        <v>0.4376</v>
       </c>
       <c r="G14" t="n">
         <v>-2.2533</v>
@@ -1522,13 +1522,13 @@
         <v>4.5776</v>
       </c>
       <c r="K14" t="n">
-        <v>4.277199999999999</v>
+        <v>4.2772</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3000999999999999</v>
+        <v>0.3001000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-6.830800000000001</v>
+        <v>-6.8308</v>
       </c>
       <c r="N14" t="n">
         <v>-7.5846</v>
@@ -1537,7 +1537,7 @@
         <v>0.7538000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.0001000000000006551</v>
+        <v>-0.000100000000000211</v>
       </c>
       <c r="Q14" t="n">
         <v>-16.2367</v>
@@ -1546,13 +1546,13 @@
         <v>16.2369</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.6534</v>
+        <v>-1.9064</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6853000000000002</v>
+        <v>0.06129999999999991</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.9679</v>
+        <v>-1.9681</v>
       </c>
       <c r="V14" t="n">
         <v>-4.935700000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.338800000000001</v>
+        <v>7.165</v>
       </c>
       <c r="E15" t="n">
-        <v>5.2508</v>
+        <v>3.9533</v>
       </c>
       <c r="F15" t="n">
-        <v>3.088</v>
+        <v>3.2116</v>
       </c>
       <c r="G15" t="n">
         <v>4.1623</v>
@@ -1624,13 +1624,13 @@
         <v>2.0876</v>
       </c>
       <c r="S15" t="n">
-        <v>3.2486</v>
+        <v>2.0748</v>
       </c>
       <c r="T15" t="n">
-        <v>2.4732</v>
+        <v>1.1758</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7754</v>
+        <v>0.899</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.746</v>
+        <v>3.7574</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0431</v>
+        <v>1.8636</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7029</v>
+        <v>1.8938</v>
       </c>
       <c r="G16" t="n">
         <v>3.3854</v>
@@ -1702,13 +1702,13 @@
         <v>2.3195</v>
       </c>
       <c r="S16" t="n">
-        <v>3.1441</v>
+        <v>2.1554</v>
       </c>
       <c r="T16" t="n">
-        <v>2.3239</v>
+        <v>1.1444</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8202</v>
+        <v>1.0111</v>
       </c>
       <c r="V16" t="n">
         <v>0.5361</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.2849</v>
+        <v>3.6046</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0808</v>
+        <v>1.1423</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2042</v>
+        <v>2.4623</v>
       </c>
       <c r="G17" t="n">
         <v>-1.1478</v>
@@ -1780,13 +1780,13 @@
         <v>1.8556</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0312</v>
+        <v>1.2885</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5228</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4916</v>
+        <v>0.7497</v>
       </c>
       <c r="V17" t="n">
         <v>1.6083</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4501</v>
+        <v>3.2967</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.9299</v>
+        <v>-1.8683</v>
       </c>
       <c r="F18" t="n">
-        <v>4.38</v>
+        <v>5.165</v>
       </c>
       <c r="G18" t="n">
         <v>-1.2709</v>
@@ -1858,13 +1858,13 @@
         <v>2.5515</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.6913</v>
+        <v>0.1553</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.2696</v>
+        <v>-0.208</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4217</v>
+        <v>0.3633</v>
       </c>
       <c r="V18" t="n">
         <v>1.8608</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. MOTLEY</t>
+          <t>C. JONES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6463</v>
+        <v>1.2437</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.505</v>
+        <v>-0.2553</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1513</v>
+        <v>1.499</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7363</v>
+        <v>1.1972</v>
       </c>
       <c r="H19" t="n">
-        <v>0.318</v>
+        <v>-0.7635</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4183</v>
+        <v>1.9607</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5076000000000001</v>
+        <v>1.6444</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.3095</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.3349</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2287</v>
+        <v>-0.4472</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1896</v>
+        <v>-1.073</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4183</v>
+        <v>0.6258</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6959</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7859</v>
+        <v>-0.8865</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.224</v>
+        <v>-0.6524</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5619</v>
+        <v>-0.2341</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.8608</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.7886</v>
+        <v>1.0722</v>
       </c>
       <c r="X19" t="n">
         <v>0.7886</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. JONES</t>
+          <t>J. MOTLEY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4916</v>
+        <v>0.865</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4912</v>
+        <v>-0.3871</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9828</v>
+        <v>1.2521</v>
       </c>
       <c r="G20" t="n">
-        <v>1.1972</v>
+        <v>0.7363</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7635</v>
+        <v>0.318</v>
       </c>
       <c r="I20" t="n">
-        <v>1.9607</v>
+        <v>0.4183</v>
       </c>
       <c r="J20" t="n">
-        <v>1.6444</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3095</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3349</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4472</v>
+        <v>0.2287</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.073</v>
+        <v>-0.1896</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6258</v>
+        <v>0.4183</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.6386</v>
+        <v>-0.5671</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8883</v>
+        <v>-0.1061</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7503</v>
+        <v>-0.461</v>
       </c>
       <c r="V20" t="n">
-        <v>1.8608</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0722</v>
+        <v>-0.7886</v>
       </c>
       <c r="X20" t="n">
         <v>0.7886</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4533</v>
+        <v>0.6448</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0635</v>
+        <v>1.2995</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6103</v>
+        <v>-0.6546999999999999</v>
       </c>
       <c r="G21" t="n">
         <v>-1.0844</v>
@@ -2092,13 +2092,13 @@
         <v>0.6959</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3058</v>
+        <v>0.4973</v>
       </c>
       <c r="T21" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.2438</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2978</v>
+        <v>0.2535</v>
       </c>
       <c r="V21" t="n">
         <v>0.5361</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. BLAKENEY</t>
+          <t>C. MALCOLM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2041</v>
+        <v>-0.4806</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0793</v>
+        <v>-3.0756</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1248</v>
+        <v>2.595</v>
       </c>
       <c r="G22" t="n">
-        <v>1.3842</v>
+        <v>-1.9645</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.587</v>
+        <v>-0.1677</v>
       </c>
       <c r="I22" t="n">
-        <v>2.9712</v>
+        <v>-1.7968</v>
       </c>
       <c r="J22" t="n">
-        <v>2.3459</v>
+        <v>-1.8925</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6820000000000001</v>
+        <v>0.3193</v>
       </c>
       <c r="L22" t="n">
-        <v>3.0279</v>
+        <v>-2.2118</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9617</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9049</v>
+        <v>-0.487</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0568</v>
+        <v>0.415</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.0876</v>
+        <v>1.1598</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3917</v>
+        <v>2.3195</v>
       </c>
       <c r="S22" t="n">
-        <v>1.4435</v>
+        <v>0.3242</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6765</v>
+        <v>-0.0233</v>
       </c>
       <c r="U22" t="n">
-        <v>0.767</v>
+        <v>0.3475</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C. MALCOLM</t>
+          <t>A. BLAKENEY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5605</v>
+        <v>-0.6989</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3115</v>
+        <v>-0.5105</v>
       </c>
       <c r="F23" t="n">
-        <v>2.751</v>
+        <v>-0.1884</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.9645</v>
+        <v>1.3842</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1677</v>
+        <v>-1.587</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.7968</v>
+        <v>2.9712</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.8925</v>
+        <v>2.3459</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3193</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.2118</v>
+        <v>3.0279</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.9617</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.487</v>
+        <v>-0.9049</v>
       </c>
       <c r="O23" t="n">
-        <v>0.415</v>
+        <v>-0.0568</v>
       </c>
       <c r="P23" t="n">
-        <v>1.1598</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R23" t="n">
-        <v>2.3195</v>
+        <v>1.3917</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2443</v>
+        <v>0.5406</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2592</v>
+        <v>0.0868</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5034999999999999</v>
+        <v>0.4538</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.499</v>
+        <v>-1.8649</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.0268</v>
+        <v>0.0911</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.4722</v>
+        <v>-1.956</v>
       </c>
       <c r="G24" t="n">
         <v>-2.0281</v>
@@ -2326,13 +2326,13 @@
         <v>0.4639</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9348</v>
+        <v>-0.3007</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4402</v>
+        <v>-0.3222</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4946</v>
+        <v>0.0215</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.6807</v>
+        <v>-2.4898</v>
       </c>
       <c r="E25" t="n">
         <v>-2.2201</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.4606</v>
+        <v>-0.2697</v>
       </c>
       <c r="G25" t="n">
         <v>-0.3836</v>
@@ -2404,13 +2404,13 @@
         <v>0.232</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2095</v>
+        <v>-0.0187</v>
       </c>
       <c r="T25" t="n">
         <v>0.08260000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2921</v>
+        <v>-0.1013</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.0327</v>
+        <v>-2.8418</v>
       </c>
       <c r="E26" t="n">
         <v>-0.4705</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.5622</v>
+        <v>-2.3714</v>
       </c>
       <c r="G26" t="n">
         <v>-0.733</v>
@@ -2482,13 +2482,13 @@
         <v>0.232</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.4415</v>
+        <v>-0.2506</v>
       </c>
       <c r="T26" t="n">
         <v>0.007900000000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.4494</v>
+        <v>-0.2585</v>
       </c>
       <c r="V26" t="n">
         <v>-0.9304</v>
@@ -2515,40 +2515,40 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>9.8422</v>
+        <v>12.2012</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.4375000000000001</v>
+        <v>-0.4375999999999994</v>
       </c>
       <c r="F27" t="n">
-        <v>10.2797</v>
+        <v>12.6386</v>
       </c>
       <c r="G27" t="n">
-        <v>2.253100000000001</v>
+        <v>2.253100000000002</v>
       </c>
       <c r="H27" t="n">
         <v>3.307200000000002</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.0538</v>
+        <v>-1.053800000000001</v>
       </c>
       <c r="J27" t="n">
         <v>6.8308</v>
       </c>
       <c r="K27" t="n">
-        <v>7.5844</v>
+        <v>7.584399999999999</v>
       </c>
       <c r="L27" t="n">
         <v>-0.7537000000000004</v>
       </c>
       <c r="M27" t="n">
-        <v>-4.577599999999999</v>
+        <v>-4.5776</v>
       </c>
       <c r="N27" t="n">
         <v>-4.277300000000001</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.3000999999999999</v>
+        <v>-0.3001</v>
       </c>
       <c r="P27" t="n">
         <v>9.999999999932285e-05</v>
@@ -2560,13 +2560,13 @@
         <v>16.2368</v>
       </c>
       <c r="S27" t="n">
-        <v>2.653499999999999</v>
+        <v>5.012499999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>1.9679</v>
+        <v>1.9681</v>
       </c>
       <c r="U27" t="n">
-        <v>0.6855000000000002</v>
+        <v>3.0445</v>
       </c>
       <c r="V27" t="n">
         <v>4.935600000000001</v>
